--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_122_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_122_R13.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5448</v>
+        <v>2.237</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3065</v>
+        <v>-0.2542</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2383</v>
+        <v>2.4913</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0334</v>
+        <v>0.045</v>
       </c>
       <c r="H2" t="n">
-        <v>1.054</v>
+        <v>-1.2531</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0873</v>
+        <v>1.2981</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9391</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1294</v>
+        <v>-0.6519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8097</v>
+        <v>1.5657</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9725</v>
+        <v>-0.8687</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0755</v>
+        <v>-0.6012</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.897</v>
+        <v>-0.2676</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-2.7834</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0937</v>
+        <v>-0.4885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5272</v>
+        <v>-1.0651</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5666</v>
+        <v>0.5766</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7886</v>
+        <v>2.6805</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0512</v>
+        <v>1.8619</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6081</v>
+        <v>0.3629</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6593</v>
+        <v>1.499</v>
       </c>
       <c r="G3" t="n">
-        <v>0.045</v>
+        <v>-0.0334</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2531</v>
+        <v>1.054</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2981</v>
+        <v>-1.0873</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9137999999999999</v>
+        <v>1.9391</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6519</v>
+        <v>1.1294</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5657</v>
+        <v>0.8097</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8687</v>
+        <v>-1.9725</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6012</v>
+        <v>-0.0755</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2676</v>
+        <v>-1.897</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6743</v>
+        <v>0.4107</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4189</v>
+        <v>-0.4165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7446</v>
+        <v>0.8272</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6805</v>
+        <v>0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.947</v>
+        <v>1.3797</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5255</v>
+        <v>0.5577</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4216</v>
+        <v>0.822</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0955</v>
+        <v>1.8004</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8355</v>
+        <v>1.1079</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9311</v>
+        <v>0.6925</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0888</v>
+        <v>2.8691</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2667</v>
+        <v>1.8555</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3555</v>
+        <v>1.0136</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0067</v>
+        <v>-1.0687</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-0.7477</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5756</v>
+        <v>-0.3211</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2278</v>
+        <v>-0.8845</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9006</v>
+        <v>-1.1516</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3273</v>
+        <v>0.2671</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7241</v>
+        <v>0.9698</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4398</v>
+        <v>0.5818</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2843</v>
+        <v>0.388</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8004</v>
+        <v>1.0955</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1079</v>
+        <v>-1.8355</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6925</v>
+        <v>2.9311</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8691</v>
+        <v>1.0888</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8555</v>
+        <v>-1.2667</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0136</v>
+        <v>2.3555</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0687</v>
+        <v>0.0067</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7477</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3211</v>
+        <v>0.5756</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5402</v>
+        <v>0.2506</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2696</v>
+        <v>-0.0431</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2706</v>
+        <v>0.2937</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0571</v>
+        <v>0.7127</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0076</v>
+        <v>0.1104</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0646</v>
+        <v>0.6024</v>
       </c>
       <c r="G6" t="n">
         <v>0.8116</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6307</v>
+        <v>-0.975</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1202</v>
+        <v>-1.0023</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5105</v>
+        <v>0.0272</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2836</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0562</v>
+        <v>-0.8868</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2121</v>
+        <v>-2.7403</v>
       </c>
       <c r="F7" t="n">
-        <v>2.156</v>
+        <v>1.8535</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7917999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.481</v>
+        <v>-0.3117</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5683</v>
+        <v>-1.0965</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0873</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>1.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4476</v>
+        <v>-3.0601</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9282</v>
+        <v>-2.5743</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5194</v>
+        <v>-0.4858</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4182</v>
@@ -1078,13 +1078,13 @@
         <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0627</v>
+        <v>-0.6752</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4936</v>
+        <v>-1.1398</v>
       </c>
       <c r="U8" t="n">
-        <v>0.431</v>
+        <v>0.4646</v>
       </c>
       <c r="V8" t="n">
         <v>-3.3584</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8557</v>
+        <v>-3.2495</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9699</v>
+        <v>-3.4981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1141</v>
+        <v>0.2485</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0819</v>
@@ -1156,13 +1156,13 @@
         <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.078</v>
+        <v>-0.4718</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.6484</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0422</v>
+        <v>0.1766</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03530000000000122</v>
+        <v>-0.03529999999999944</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.454099999999999</v>
+        <v>-7.454100000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>7.418800000000001</v>
+        <v>7.418900000000001</v>
       </c>
       <c r="G10" t="n">
         <v>0.4272</v>
@@ -1237,10 +1237,10 @@
         <v>-3.1454</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.563000000000001</v>
+        <v>-6.563299999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>3.417899999999999</v>
+        <v>3.4178</v>
       </c>
       <c r="V10" t="n">
         <v>0.3632</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.0553</v>
+        <v>4.1482</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0424</v>
+        <v>1.9582</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0129</v>
+        <v>2.1901</v>
       </c>
       <c r="G11" t="n">
-        <v>3.662</v>
+        <v>2.1978</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9025</v>
+        <v>2.4453</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7595</v>
+        <v>-0.2475</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9091</v>
+        <v>2.7624</v>
       </c>
       <c r="K11" t="n">
-        <v>3.146</v>
+        <v>2.6888</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7631</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2472</v>
+        <v>-0.5646</v>
       </c>
       <c r="N11" t="n">
         <v>-0.2435</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0037</v>
+        <v>-0.3211</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1794</v>
+        <v>0.7185</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2388</v>
+        <v>-0.1806</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9405</v>
+        <v>0.899</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.024</v>
+        <v>3.9601</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6659</v>
+        <v>3.9809</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3581</v>
+        <v>-0.0207</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1978</v>
+        <v>3.662</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4453</v>
+        <v>2.9025</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2475</v>
+        <v>0.7595</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7624</v>
+        <v>4.9091</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6888</v>
+        <v>3.146</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0736</v>
+        <v>1.7631</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5646</v>
+        <v>-1.2472</v>
       </c>
       <c r="N12" t="n">
         <v>-0.2435</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3211</v>
+        <v>-1.0037</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5942</v>
+        <v>1.0842</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5272</v>
+        <v>0.1772</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0671</v>
+        <v>0.9069</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3099</v>
+        <v>1.6466</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0549</v>
+        <v>0.181</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3648</v>
+        <v>1.4656</v>
       </c>
       <c r="G13" t="n">
         <v>0.7040999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.322</v>
+        <v>0.0147</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1593</v>
+        <v>1.0914</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4219</v>
+        <v>1.186</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2626</v>
+        <v>-0.0946</v>
       </c>
       <c r="G14" t="n">
         <v>2.4978</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2851</v>
+        <v>0.2172</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2155</v>
+        <v>0.5193</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0127</v>
+        <v>0.4591</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2282</v>
+        <v>0.0602</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6591</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1788</v>
+        <v>0.4826</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8509</v>
+        <v>0.6829</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2039</v>
+        <v>0.4899</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.9359</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6141</v>
+        <v>-0.446</v>
       </c>
       <c r="G16" t="n">
         <v>1.0736</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2614</v>
+        <v>0.0246</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U16" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5976</v>
+        <v>-0.6642</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3731</v>
+        <v>-2.1372</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7755</v>
+        <v>1.473</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2175</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.076</v>
+        <v>-0.1426</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8202</v>
+        <v>0.5177</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8664</v>
+        <v>-1.7313</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0324</v>
+        <v>-0.7965</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.834</v>
+        <v>-0.9348</v>
       </c>
       <c r="G18" t="n">
         <v>1.2087</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3071</v>
+        <v>-0.172</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6083</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6729</v>
+        <v>-2.4165</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8658</v>
+        <v>-3.385</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1929</v>
+        <v>0.9685</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1787</v>
+        <v>-0.362</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7166</v>
+        <v>-0.2581</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.462</v>
+        <v>-0.1039</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1203</v>
+        <v>0.5814</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4516</v>
+        <v>-0.1611</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3312</v>
+        <v>0.7425</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0583</v>
+        <v>-0.9434</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2651</v>
+        <v>-0.097</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7933</v>
+        <v>-0.8464</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4747</v>
+        <v>0.3372</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0791</v>
+        <v>-0.4872</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3957</v>
+        <v>0.8244</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5051</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.5051</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3595</v>
+        <v>-3.38</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0927</v>
+        <v>-4.3376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7332</v>
+        <v>0.9577</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.362</v>
+        <v>-3.1787</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2581</v>
+        <v>-1.7166</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1039</v>
+        <v>-1.462</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5814</v>
+        <v>-1.1203</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1611</v>
+        <v>-1.4516</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7425</v>
+        <v>0.3312</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9434</v>
+        <v>-2.0583</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.097</v>
+        <v>-0.2651</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8464</v>
+        <v>-1.7933</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6058</v>
+        <v>0.7677</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>-0.3927</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5891</v>
+        <v>1.1604</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-0.5051</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.5051</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4362</v>
+        <v>-3.6283</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9354</v>
+        <v>-5.4636</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4993</v>
+        <v>1.8353</v>
       </c>
       <c r="G21" t="n">
         <v>-4.354</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9946</v>
+        <v>-0.1867</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1202</v>
+        <v>-0.6484</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1256</v>
+        <v>0.4617</v>
       </c>
       <c r="V21" t="n">
         <v>1.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03530000000000033</v>
+        <v>0.03519999999999923</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.418800000000001</v>
+        <v>-7.418799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>7.4542</v>
+        <v>7.4543</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4272999999999998</v>
@@ -2152,13 +2152,13 @@
         <v>5.034599999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.7372</v>
+        <v>-8.737200000000001</v>
       </c>
       <c r="N22" t="n">
         <v>-1.5949</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.1425</v>
+        <v>-7.142499999999999</v>
       </c>
       <c r="P22" t="n">
         <v>-2.3195</v>
@@ -2170,13 +2170,13 @@
         <v>13.9173</v>
       </c>
       <c r="S22" t="n">
-        <v>3.145299999999999</v>
+        <v>3.1454</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.4177</v>
+        <v>-3.4179</v>
       </c>
       <c r="U22" t="n">
-        <v>6.5632</v>
+        <v>6.5631</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3633</v>
